--- a/backend/wp_templates/K/K3 其他应付款.xlsx
+++ b/backend/wp_templates/K/K3 其他应付款.xlsx
@@ -13917,7 +13917,7 @@
       <c r="R10" s="19"/>
       <c r="S10" s="19"/>
       <c r="T10" s="191">
-        <f>O10+R10+S10</f>
+        <f>Q10+R10+S10</f>
         <v>0</v>
       </c>
       <c r="U10" s="18"/>
@@ -13958,7 +13958,7 @@
       <c r="R11" s="19"/>
       <c r="S11" s="19"/>
       <c r="T11" s="191">
-        <f t="shared" ref="T11:T30" si="3">O11+R11+S11</f>
+        <f t="shared" ref="T11:T30" si="3">Q11+R11+S11</f>
         <v>0</v>
       </c>
       <c r="U11" s="18"/>
